--- a/PREF.xlsx
+++ b/PREF.xlsx
@@ -8,20 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nagu/Desktop/NVZ_SKD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DFE05F3-024D-B44F-8334-E8F769C6264F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9AEB5B-2C8C-9B47-A7F0-E8CE33BBB595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17160" yWindow="1020" windowWidth="16880" windowHeight="21080" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="色分け設定" sheetId="1" r:id="rId1"/>
-    <sheet name="抽出変換設定" sheetId="2" r:id="rId2"/>
+    <sheet name="SIMSLOT" sheetId="3" r:id="rId2"/>
+    <sheet name="抽出変換設定" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="78">
   <si>
     <t>対象文字列</t>
   </si>
@@ -249,6 +263,12 @@
   </si>
   <si>
     <t>EXPAT GJ</t>
+  </si>
+  <si>
+    <t>SIM-SLOT使用対象訓練(一行目)</t>
+  </si>
+  <si>
+    <t>CMD,RMD,SCCS,OJTS,CARQ,CARF,CATR,FORF,FOTR,DTY,VLDP,ATRN,VLDA,CAUG,PH3,VLDE,OTHR,ISR,GS-R,M11,M12,M21,M22,CAT12,CAT3,DTY,NXZE</t>
   </si>
 </sst>
 </file>
@@ -731,7 +751,11 @@
   <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="6" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="41" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="36.5" customWidth="1"/>
+    <col min="5" max="6" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1154,6 +1178,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE8D720-6B51-E542-932C-E4AAB619F301}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>

--- a/PREF.xlsx
+++ b/PREF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nagu/Desktop/NVZ_SKD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9AEB5B-2C8C-9B47-A7F0-E8CE33BBB595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A5C6BD-B52A-F747-835E-489FBC2F6F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17160" yWindow="1020" windowWidth="16880" windowHeight="21080" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -268,7 +268,8 @@
     <t>SIM-SLOT使用対象訓練(一行目)</t>
   </si>
   <si>
-    <t>CMD,RMD,SCCS,OJTS,CARQ,CARF,CATR,FORF,FOTR,DTY,VLDP,ATRN,VLDA,CAUG,PH3,VLDE,OTHR,ISR,GS-R,M11,M12,M21,M22,CAT12,CAT3,DTY,NXZE</t>
+    <t>CMD,RMD,SCCS,OJTS,CARQ,CARF,CATR,FORF,FOTR,DTY,VLDP,ATRN,VLDA,CAUG,PH3,VLDE,OTHR,ISR,GS-R,M11,M12,M21,M22,CAT12,CAT3,DTY,NXZE,SSQ</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>

--- a/PREF.xlsx
+++ b/PREF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nagu/Desktop/NVZ_SKD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA214348-0CA9-EB44-B491-6864F609D1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A986CDB4-884F-9C4B-93B8-19957301D441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8980" yWindow="860" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8980" yWindow="860" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="色分け設定" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="875">
   <si>
     <t>対象文字列</t>
   </si>
@@ -2682,6 +2682,10 @@
   </si>
   <si>
     <t>啓</t>
+  </si>
+  <si>
+    <t>NVB001</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -3655,7 +3659,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>874</v>
       </c>
       <c r="B2" t="s">
         <v>87</v>

--- a/PREF.xlsx
+++ b/PREF.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nagu/Desktop/NVZ_SKD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A986CDB4-884F-9C4B-93B8-19957301D441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EFB8DB-3B46-F14C-8C52-FA4284C27CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8980" yWindow="860" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="色分け設定" sheetId="1" r:id="rId1"/>
     <sheet name="SIMSLOT" sheetId="3" r:id="rId2"/>
     <sheet name="emp_no" sheetId="4" r:id="rId3"/>
-    <sheet name="抽出変換設定" sheetId="2" r:id="rId4"/>
+    <sheet name="SKD抽出用" sheetId="5" r:id="rId4"/>
+    <sheet name="抽出変換設定" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="emp_no" localSheetId="2">emp_no!$A$1:$I$392</definedName>
@@ -58,8 +59,30 @@
 </connections>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="876">
   <si>
     <t>対象文字列</t>
   </si>
@@ -2685,6 +2708,67 @@
   </si>
   <si>
     <t>NVB001</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">名簿にある乗員だけのリストを作成するには以下の職員番号をコピペしてJasper Reportでスケジュール抽出してください。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">その際[FLEET]（350,787など）を選ぶのを忘れないでください。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>全乗員のスケジュールを整形する場合はFLEETのみ選択でOKです。（時間がかかります。）</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">メイボニアル </t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t xml:space="preserve">ジョウインダケノリストヲ </t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t xml:space="preserve">サクセイスルニハ </t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t xml:space="preserve">イカノ </t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t xml:space="preserve">ショクインバンゴウヲ </t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t xml:space="preserve">エラブノヲ </t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t xml:space="preserve">ワスレナイデクダサイ </t>
+    </rPh>
+    <rPh sb="100" eb="103">
+      <t xml:space="preserve">ゼンジョウインヲ </t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t xml:space="preserve">セイケイスルバアイハ </t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t xml:space="preserve">センタクデ </t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t xml:space="preserve">ジカンガカカリマス </t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2692,7 +2776,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2712,6 +2796,35 @@
       <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -2826,7 +2939,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2852,6 +2965,15 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -12684,6 +12806,58 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA02B1F-9C6A-F043-8E69-5FE5B9EB8AD5}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="60" customHeight="1">
+      <c r="A1" s="19" t="s">
+        <v>875</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+    </row>
+    <row r="2" spans="1:14" ht="409" customHeight="1">
+      <c r="A2" s="21" t="str" cm="1">
+        <f t="array" ref="A2">_xlfn.TEXTJOIN(",", TRUE, IF(emp_no!C2:INDEX(emp_no!C:C, LOOKUP(2,1/(emp_no!C:C&lt;&gt;""), ROW(emp_no!C:C)))&lt;&gt;"", "000"&amp;emp_no!C2:INDEX(emp_no!C:C, LOOKUP(2,1/(emp_no!C:C&lt;&gt;""), ROW(emp_no!C:C))), ""))</f>
+        <v>00039680,00049147,00041511,00046107,00041672,00045104,00038579,00041492,00041478,00041331,00041271,00041675,00042420,00045105,00048688,00038564,00041571,00041333,00050842,00045585,00041554,00041339,00041371,00041850,00042072,00049580,00040592,00041334,00036758,00041205,00041512,00041493,00043014,00044484,00046104,00053806,00042725,00044009,00044007,00045117,00048783,00039615,00049043,00039645,00041268,00041668,00044005,00048143,00036756,00036777,00037756,00037761,00048687,00040593,00049290,00041396,00041556,00041337,00049148,00041498,00042073,00041507,00042075,00044397,00042422,00043854,00043861,00040618,00040568,00038587,00041685,00067838,00047991,00036147,00037243,00038260,00039243,00037741,00037726,00037750,00039617,00038569,00038593,00042244,00048673,00048684,00041317,00041323,00041661,00049111,00043652,00044966,00037706,00067673,00067393,00067851,00067904,00036184,00037238,00039665,00039684,00041283,00049121,00041484,00053747,00035740,00035216,00037743,00037732,00041486,00052461,00056911,00055023,00056895,00052215,00053894,00052029,00036963,00039238,00039668,00042423,00053768,00053787,00046043,00050843,00051138,00052467,00055022,00057515,00056893,00053861,00052212,00053803,00036185,00053733,00039671,00048682,00049136,00053759,00053849,00045116,00045154,00054386,00058950,00056900,00057462,00053807,00052196,00052209,00045618,00036965,00040560,00041304,00049411,00042084,00041705,00044415,00053816,00045589,00045960,00056565,00054373,00055007,00056894,00057472,00052193,00044492,00052011,00067337,00037698,00040781,00053740,00040612,00042419,00045108,00045152,00050880,00051140,00057243,00055045,00056896,00057464,00053858,00052213,00053901,00041666,00044490,00037716,00039646,00038575,00040620,00043461,00042247,00045586,00045619,00045950,00054376,00058951,00056866,00052189,00052586,00045588,00052031,00036150,00036968,00049074,00039673,00040624,00041181,00053767,00044962,00045587,00041206,00056581,00055025,00056873,00057449,00053855,00052211,00053902,00051354,00039630,00037763,00039667,00053735,00041191,00041703,00044983,00045151,00045621,00054377,00055013,00057497,00053857,00052214,00045150,00050879,00053805,00067836,00039611,00040970,00039633,00040611,00041742,00046041,00045957,00054378,00056853,00056865,00057498,00052191,00052207,00052587,00035738,00038568,00039683,00041187,00053781,00041696,00044388,00044975,00044493,00052012,00056617,00054367,00056912,00056864,00056860,00053863,00053898,00051139,00048174,00040790,00048678,00040563,00053732,00050290,00044977,00050841,00051355,00054374,00056877,00058953,00053860,00052210,00053895,00051290,00036754,00038537,00038546,00048680,00053742,00041325,00044974,00046106,00046039,00051289,00052465,00055050,00056876,00057490,00052190,00049582,00053802,00036971,00037729,00038583,00041188,00049410,00042724,00044950,00045115,00045584,00056692,00057247,00055044,00056862,00056882,00057511,00052188,00053892,00053810,00067852,00035737,00040259,00038559,00041468,00044952,00045593,00045149,00045617,00052463,00056849,00054381,00057244,00056906,00057459,00052192,00052030,00067753,00038262,00039357,00049155,00049394,00049332,00044530,00045118,00050881,00045616,00054385,00055036,00058952,00053859,00052195,00052032,00048026,00049047,00040783,00048691,00053739,00043862,00044486,00046040,00051326,00040973,00040599,00044396,00045113,00051291,00041336,00045114,00038590,00036748,00039641,00039681,00039629,00041204,00048993,00040269,00044394,00057451,00056897,00057454,00057471,00057510,00057483,00057460,00058367,00053896,00057475,00057484</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>

--- a/PREF.xlsx
+++ b/PREF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10718"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nagu/Desktop/NVZ_SKD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EFB8DB-3B46-F14C-8C52-FA4284C27CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{9F616CD4-61F9-2B4A-9471-9CFB86F24659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="色分け設定" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="emp_no" localSheetId="2">emp_no!$A$1:$I$392</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,8 +41,8 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{763F14B1-D4C4-CF4E-B405-49F8C87781C7}" name="emp_no" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="65001" sourceFile="/Users/nagu/Desktop/NVZ_SKD/emp_no.csv" comma="1">
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="emp_no" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/nagu/Desktop/NVZ_SKD/emp_no.csv" comma="1">
       <textFields count="9">
         <textField/>
         <textField/>
@@ -2776,7 +2776,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3003,7 +3003,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="emp_no" connectionId="1" xr16:uid="{26AE79F9-3D17-0D43-B67C-ECA6649B0260}" autoFormatId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="emp_no" connectionId="1" xr16:uid="{00000000-0016-0000-0200-000000000000}" autoFormatId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3292,16 +3292,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="41" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="36.5" customWidth="1"/>
-    <col min="5" max="6" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" customWidth="1"/>
+    <col min="2" max="2" width="41.04296875" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
+    <col min="4" max="4" width="36.54296875" customWidth="1"/>
+    <col min="5" max="6" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -3321,7 +3321,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F11" s="11"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="F12" s="12"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A13" s="3" t="s">
         <v>18</v>
       </c>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="F13" s="12"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A14" s="3" t="s">
         <v>18</v>
       </c>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="F14" s="12"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A15" s="3" t="s">
         <v>18</v>
       </c>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="F16" s="12"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A17" s="3" t="s">
         <v>18</v>
       </c>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="F17" s="13"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="F18" s="14"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="F19" s="14"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="F20" s="15"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="F21" s="16"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A22" s="3" t="s">
         <v>18</v>
       </c>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="F22" s="17"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A23" s="3" t="s">
         <v>18</v>
       </c>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="F23" s="17"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A24" s="3" t="s">
         <v>18</v>
       </c>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="F24" s="14"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A25" s="3" t="s">
         <v>18</v>
       </c>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="F25" s="14"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A26" s="3" t="s">
         <v>18</v>
       </c>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A27" s="3" t="s">
         <v>18</v>
       </c>
@@ -3723,9 +3723,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE8D720-6B51-E542-932C-E4AAB619F301}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.1">
       <c r="A1" t="s">
         <v>76</v>
       </c>
@@ -3742,18 +3742,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{991C2738-FE3E-A04F-890B-D204239BC212}">
   <dimension ref="A1:I392"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="7.49609375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.04296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.99609375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A1" t="s">
         <v>78</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A2" t="s">
         <v>874</v>
       </c>
@@ -3802,7 +3802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A4" t="s">
         <v>95</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A5" t="s">
         <v>99</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A6" t="s">
         <v>103</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A7" t="s">
         <v>107</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A8" t="s">
         <v>111</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A9" t="s">
         <v>115</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A10" t="s">
         <v>119</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A11" t="s">
         <v>123</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A12" t="s">
         <v>127</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A13" t="s">
         <v>130</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A14" t="s">
         <v>133</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A15" t="s">
         <v>137</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A16" t="s">
         <v>140</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A17" t="s">
         <v>143</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A18" t="s">
         <v>146</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A19" t="s">
         <v>115</v>
       </c>
@@ -4199,7 +4199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A20" t="s">
         <v>130</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A21" t="s">
         <v>140</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A22" t="s">
         <v>86</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A23" t="s">
         <v>99</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A24" t="s">
         <v>91</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A25" t="s">
         <v>119</v>
       </c>
@@ -4373,7 +4373,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A27" t="s">
         <v>95</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A28" t="s">
         <v>130</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A29" t="s">
         <v>140</v>
       </c>
@@ -4489,7 +4489,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A30" t="s">
         <v>177</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A31" t="s">
         <v>177</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A32" t="s">
         <v>177</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A33" t="s">
         <v>177</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A34" t="s">
         <v>177</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A35" t="s">
         <v>177</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A36" t="s">
         <v>177</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A37" t="s">
         <v>177</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A38" t="s">
         <v>198</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A39" t="s">
         <v>198</v>
       </c>
@@ -4725,7 +4725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A40" t="s">
         <v>198</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A41" t="s">
         <v>198</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A42" t="s">
         <v>198</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A43" t="s">
         <v>198</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A44" t="s">
         <v>198</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A45" t="s">
         <v>198</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A46" t="s">
         <v>198</v>
       </c>
@@ -4907,7 +4907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A47" t="s">
         <v>198</v>
       </c>
@@ -4933,7 +4933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A48" t="s">
         <v>198</v>
       </c>
@@ -4959,7 +4959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A49" t="s">
         <v>198</v>
       </c>
@@ -4985,7 +4985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A50" t="s">
         <v>198</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A51" t="s">
         <v>198</v>
       </c>
@@ -5037,7 +5037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A52" t="s">
         <v>198</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A53" t="s">
         <v>198</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A54" t="s">
         <v>198</v>
       </c>
@@ -5115,7 +5115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A55" t="s">
         <v>198</v>
       </c>
@@ -5141,7 +5141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A56" t="s">
         <v>198</v>
       </c>
@@ -5167,7 +5167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A57" t="s">
         <v>198</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A58" t="s">
         <v>198</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A59" t="s">
         <v>198</v>
       </c>
@@ -5245,7 +5245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A60" t="s">
         <v>198</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A61" t="s">
         <v>198</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A62" t="s">
         <v>198</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A63" t="s">
         <v>198</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A64" t="s">
         <v>198</v>
       </c>
@@ -5375,7 +5375,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A65" t="s">
         <v>198</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A66" t="s">
         <v>198</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A67" t="s">
         <v>198</v>
       </c>
@@ -5453,7 +5453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A68" t="s">
         <v>198</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A69" t="s">
         <v>198</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A70" t="s">
         <v>198</v>
       </c>
@@ -5531,7 +5531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A71" t="s">
         <v>198</v>
       </c>
@@ -5557,7 +5557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A72" t="s">
         <v>198</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A73" t="s">
         <v>198</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A74" t="s">
         <v>198</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A75" t="s">
         <v>198</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A76" t="s">
         <v>198</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A77" t="s">
         <v>198</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A78" t="s">
         <v>198</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A79" t="s">
         <v>198</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A80" t="s">
         <v>198</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A81" t="s">
         <v>198</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A82" t="s">
         <v>198</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A83" t="s">
         <v>198</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A84" t="s">
         <v>198</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A85" t="s">
         <v>198</v>
       </c>
@@ -5921,7 +5921,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A86" t="s">
         <v>198</v>
       </c>
@@ -5947,7 +5947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A87" t="s">
         <v>198</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A88" t="s">
         <v>198</v>
       </c>
@@ -5999,7 +5999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A89" t="s">
         <v>198</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A91" t="s">
         <v>198</v>
       </c>
@@ -6077,7 +6077,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A92" t="s">
         <v>198</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A93" t="s">
         <v>198</v>
       </c>
@@ -6123,7 +6123,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A94" t="s">
         <v>323</v>
       </c>
@@ -6146,7 +6146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A95" t="s">
         <v>323</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A96" t="s">
         <v>323</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A97" t="s">
         <v>323</v>
       </c>
@@ -6215,7 +6215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A98" t="s">
         <v>323</v>
       </c>
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A99" t="s">
         <v>323</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A100" t="s">
         <v>323</v>
       </c>
@@ -6284,7 +6284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A101" t="s">
         <v>323</v>
       </c>
@@ -6307,7 +6307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A102" t="s">
         <v>323</v>
       </c>
@@ -6330,7 +6330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A103" t="s">
         <v>323</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A104" t="s">
         <v>323</v>
       </c>
@@ -6376,7 +6376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A105" t="s">
         <v>323</v>
       </c>
@@ -6399,7 +6399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A106" t="s">
         <v>349</v>
       </c>
@@ -6419,7 +6419,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A107" t="s">
         <v>352</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A108" t="s">
         <v>352</v>
       </c>
@@ -6459,7 +6459,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A109" t="s">
         <v>352</v>
       </c>
@@ -6479,7 +6479,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A110" t="s">
         <v>352</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A111" t="s">
         <v>362</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.1">
       <c r="A112" t="s">
         <v>86</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A113" t="s">
         <v>86</v>
       </c>
@@ -6571,7 +6571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A114" t="s">
         <v>86</v>
       </c>
@@ -6597,7 +6597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A115" t="s">
         <v>86</v>
       </c>
@@ -6623,7 +6623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A116" t="s">
         <v>86</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A117" t="s">
         <v>86</v>
       </c>
@@ -6675,7 +6675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A118" t="s">
         <v>86</v>
       </c>
@@ -6701,7 +6701,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A119" t="s">
         <v>86</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A120" t="s">
         <v>86</v>
       </c>
@@ -6741,7 +6741,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A121" t="s">
         <v>86</v>
       </c>
@@ -6761,7 +6761,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A122" t="s">
         <v>86</v>
       </c>
@@ -6781,7 +6781,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A123" t="s">
         <v>86</v>
       </c>
@@ -6801,7 +6801,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A124" t="s">
         <v>86</v>
       </c>
@@ -6821,7 +6821,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A125" t="s">
         <v>86</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A126" t="s">
         <v>86</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A127" t="s">
         <v>86</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A128" t="s">
         <v>99</v>
       </c>
@@ -6907,7 +6907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A129" t="s">
         <v>99</v>
       </c>
@@ -6933,7 +6933,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A130" t="s">
         <v>99</v>
       </c>
@@ -6959,7 +6959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A131" t="s">
         <v>99</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A132" t="s">
         <v>99</v>
       </c>
@@ -7011,7 +7011,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A133" t="s">
         <v>99</v>
       </c>
@@ -7037,7 +7037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A134" t="s">
         <v>99</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A135" t="s">
         <v>99</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A136" t="s">
         <v>99</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A137" t="s">
         <v>99</v>
       </c>
@@ -7123,7 +7123,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A138" t="s">
         <v>99</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A139" t="s">
         <v>99</v>
       </c>
@@ -7163,7 +7163,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A140" t="s">
         <v>99</v>
       </c>
@@ -7183,7 +7183,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A141" t="s">
         <v>99</v>
       </c>
@@ -7203,7 +7203,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A142" t="s">
         <v>99</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A143" t="s">
         <v>99</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A144" t="s">
         <v>103</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A145" t="s">
         <v>103</v>
       </c>
@@ -7295,7 +7295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A146" t="s">
         <v>103</v>
       </c>
@@ -7321,7 +7321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A147" t="s">
         <v>103</v>
       </c>
@@ -7347,7 +7347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A148" t="s">
         <v>103</v>
       </c>
@@ -7373,7 +7373,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A149" t="s">
         <v>103</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A150" t="s">
         <v>103</v>
       </c>
@@ -7425,7 +7425,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A151" t="s">
         <v>103</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A152" t="s">
         <v>103</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A153" t="s">
         <v>103</v>
       </c>
@@ -7491,7 +7491,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A154" t="s">
         <v>103</v>
       </c>
@@ -7511,7 +7511,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A155" t="s">
         <v>103</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A156" t="s">
         <v>103</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A157" t="s">
         <v>103</v>
       </c>
@@ -7571,7 +7571,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A158" t="s">
         <v>103</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A159" t="s">
         <v>103</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A160" t="s">
         <v>103</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A161" t="s">
         <v>103</v>
       </c>
@@ -7651,7 +7651,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A162" t="s">
         <v>107</v>
       </c>
@@ -7677,7 +7677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A163" t="s">
         <v>107</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A164" t="s">
         <v>107</v>
       </c>
@@ -7729,7 +7729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A165" t="s">
         <v>107</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A166" t="s">
         <v>107</v>
       </c>
@@ -7781,7 +7781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A167" t="s">
         <v>107</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A168" t="s">
         <v>107</v>
       </c>
@@ -7833,7 +7833,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A169" t="s">
         <v>107</v>
       </c>
@@ -7859,7 +7859,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A170" t="s">
         <v>107</v>
       </c>
@@ -7879,7 +7879,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A171" t="s">
         <v>107</v>
       </c>
@@ -7899,7 +7899,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A172" t="s">
         <v>107</v>
       </c>
@@ -7919,7 +7919,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A173" t="s">
         <v>107</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A174" t="s">
         <v>107</v>
       </c>
@@ -7959,7 +7959,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A175" t="s">
         <v>107</v>
       </c>
@@ -7979,7 +7979,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A176" t="s">
         <v>107</v>
       </c>
@@ -7999,7 +7999,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A177" t="s">
         <v>107</v>
       </c>
@@ -8019,7 +8019,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A178" t="s">
         <v>107</v>
       </c>
@@ -8039,7 +8039,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A179" t="s">
         <v>107</v>
       </c>
@@ -8059,7 +8059,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A180" t="s">
         <v>111</v>
       </c>
@@ -8085,7 +8085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A181" t="s">
         <v>111</v>
       </c>
@@ -8111,7 +8111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A182" t="s">
         <v>111</v>
       </c>
@@ -8137,7 +8137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A183" t="s">
         <v>111</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A184" t="s">
         <v>111</v>
       </c>
@@ -8189,7 +8189,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A185" t="s">
         <v>111</v>
       </c>
@@ -8215,7 +8215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A186" t="s">
         <v>111</v>
       </c>
@@ -8241,7 +8241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A187" t="s">
         <v>111</v>
       </c>
@@ -8267,7 +8267,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A188" t="s">
         <v>111</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A189" t="s">
         <v>111</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A190" t="s">
         <v>111</v>
       </c>
@@ -8333,7 +8333,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A191" t="s">
         <v>111</v>
       </c>
@@ -8353,7 +8353,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A192" t="s">
         <v>111</v>
       </c>
@@ -8373,7 +8373,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A193" t="s">
         <v>111</v>
       </c>
@@ -8393,7 +8393,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A194" t="s">
         <v>111</v>
       </c>
@@ -8413,7 +8413,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A195" t="s">
         <v>111</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A196" t="s">
         <v>111</v>
       </c>
@@ -8453,7 +8453,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A197" t="s">
         <v>111</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A198" t="s">
         <v>91</v>
       </c>
@@ -8499,7 +8499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A199" t="s">
         <v>91</v>
       </c>
@@ -8525,7 +8525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A200" t="s">
         <v>91</v>
       </c>
@@ -8551,7 +8551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A201" t="s">
         <v>91</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A202" t="s">
         <v>91</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A203" t="s">
         <v>91</v>
       </c>
@@ -8629,7 +8629,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A204" t="s">
         <v>91</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A205" t="s">
         <v>91</v>
       </c>
@@ -8675,7 +8675,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A206" t="s">
         <v>91</v>
       </c>
@@ -8695,7 +8695,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A207" t="s">
         <v>91</v>
       </c>
@@ -8715,7 +8715,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A208" t="s">
         <v>91</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A209" t="s">
         <v>91</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A210" t="s">
         <v>91</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A211" t="s">
         <v>91</v>
       </c>
@@ -8795,7 +8795,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A212" t="s">
         <v>91</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A213" t="s">
         <v>91</v>
       </c>
@@ -8835,7 +8835,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A214" t="s">
         <v>91</v>
       </c>
@@ -8855,7 +8855,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A215" t="s">
         <v>115</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A216" t="s">
         <v>115</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A217" t="s">
         <v>115</v>
       </c>
@@ -8933,7 +8933,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A218" t="s">
         <v>115</v>
       </c>
@@ -8959,7 +8959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A219" t="s">
         <v>115</v>
       </c>
@@ -8985,7 +8985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A220" t="s">
         <v>115</v>
       </c>
@@ -9011,7 +9011,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A221" t="s">
         <v>115</v>
       </c>
@@ -9037,7 +9037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A222" t="s">
         <v>115</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A223" t="s">
         <v>115</v>
       </c>
@@ -9083,7 +9083,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A224" t="s">
         <v>115</v>
       </c>
@@ -9103,7 +9103,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A225" t="s">
         <v>115</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A226" t="s">
         <v>115</v>
       </c>
@@ -9143,7 +9143,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A227" t="s">
         <v>115</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A228" t="s">
         <v>115</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A229" t="s">
         <v>115</v>
       </c>
@@ -9203,7 +9203,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A230" t="s">
         <v>115</v>
       </c>
@@ -9223,7 +9223,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A231" t="s">
         <v>115</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A232" t="s">
         <v>119</v>
       </c>
@@ -9269,7 +9269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A233" t="s">
         <v>119</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A234" t="s">
         <v>119</v>
       </c>
@@ -9321,7 +9321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A235" t="s">
         <v>119</v>
       </c>
@@ -9347,7 +9347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A236" t="s">
         <v>119</v>
       </c>
@@ -9373,7 +9373,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A237" t="s">
         <v>119</v>
       </c>
@@ -9399,7 +9399,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A238" t="s">
         <v>119</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A239" t="s">
         <v>119</v>
       </c>
@@ -9445,7 +9445,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A240" t="s">
         <v>119</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A241" t="s">
         <v>119</v>
       </c>
@@ -9485,7 +9485,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A242" t="s">
         <v>119</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A243" t="s">
         <v>119</v>
       </c>
@@ -9525,7 +9525,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A244" t="s">
         <v>119</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A245" t="s">
         <v>119</v>
       </c>
@@ -9565,7 +9565,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A246" t="s">
         <v>119</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A247" t="s">
         <v>119</v>
       </c>
@@ -9605,7 +9605,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A248" t="s">
         <v>123</v>
       </c>
@@ -9631,7 +9631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A249" t="s">
         <v>123</v>
       </c>
@@ -9657,7 +9657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A250" t="s">
         <v>123</v>
       </c>
@@ -9683,7 +9683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A251" t="s">
         <v>123</v>
       </c>
@@ -9709,7 +9709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="1:8">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A252" t="s">
         <v>123</v>
       </c>
@@ -9735,7 +9735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A253" t="s">
         <v>123</v>
       </c>
@@ -9761,7 +9761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A254" t="s">
         <v>123</v>
       </c>
@@ -9787,7 +9787,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A255" t="s">
         <v>123</v>
       </c>
@@ -9807,7 +9807,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A256" t="s">
         <v>123</v>
       </c>
@@ -9827,7 +9827,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A257" t="s">
         <v>123</v>
       </c>
@@ -9847,7 +9847,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A258" t="s">
         <v>123</v>
       </c>
@@ -9867,7 +9867,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A259" t="s">
         <v>123</v>
       </c>
@@ -9887,7 +9887,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A260" t="s">
         <v>123</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="261" spans="1:8">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A261" t="s">
         <v>123</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="262" spans="1:8">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A262" t="s">
         <v>123</v>
       </c>
@@ -9947,7 +9947,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A263" t="s">
         <v>123</v>
       </c>
@@ -9967,7 +9967,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A264" t="s">
         <v>123</v>
       </c>
@@ -9987,7 +9987,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A265" t="s">
         <v>127</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A266" t="s">
         <v>127</v>
       </c>
@@ -10039,7 +10039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A267" t="s">
         <v>127</v>
       </c>
@@ -10065,7 +10065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="1:8">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A268" t="s">
         <v>127</v>
       </c>
@@ -10091,7 +10091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A269" t="s">
         <v>127</v>
       </c>
@@ -10117,7 +10117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A270" t="s">
         <v>127</v>
       </c>
@@ -10143,7 +10143,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="271" spans="1:8">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A271" t="s">
         <v>127</v>
       </c>
@@ -10169,7 +10169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="272" spans="1:8">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A272" t="s">
         <v>127</v>
       </c>
@@ -10189,7 +10189,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="273" spans="1:8">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A273" t="s">
         <v>127</v>
       </c>
@@ -10209,7 +10209,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="274" spans="1:8">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A274" t="s">
         <v>127</v>
       </c>
@@ -10229,7 +10229,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="275" spans="1:8">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A275" t="s">
         <v>127</v>
       </c>
@@ -10249,7 +10249,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="276" spans="1:8">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A276" t="s">
         <v>127</v>
       </c>
@@ -10269,7 +10269,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A277" t="s">
         <v>127</v>
       </c>
@@ -10289,7 +10289,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A278" t="s">
         <v>127</v>
       </c>
@@ -10309,7 +10309,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A279" t="s">
         <v>127</v>
       </c>
@@ -10329,7 +10329,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A280" t="s">
         <v>127</v>
       </c>
@@ -10349,7 +10349,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="281" spans="1:8">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A281" t="s">
         <v>127</v>
       </c>
@@ -10369,7 +10369,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="282" spans="1:8">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A282" t="s">
         <v>95</v>
       </c>
@@ -10395,7 +10395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:8">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A283" t="s">
         <v>95</v>
       </c>
@@ -10421,7 +10421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="1:8">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A284" t="s">
         <v>95</v>
       </c>
@@ -10447,7 +10447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:8">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A285" t="s">
         <v>95</v>
       </c>
@@ -10473,7 +10473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="286" spans="1:8">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A286" t="s">
         <v>95</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="1:8">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A287" t="s">
         <v>95</v>
       </c>
@@ -10525,7 +10525,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="288" spans="1:8">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A288" t="s">
         <v>95</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="289" spans="1:8">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A289" t="s">
         <v>95</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="290" spans="1:8">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A290" t="s">
         <v>95</v>
       </c>
@@ -10591,7 +10591,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="291" spans="1:8">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A291" t="s">
         <v>95</v>
       </c>
@@ -10611,7 +10611,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="292" spans="1:8">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A292" t="s">
         <v>95</v>
       </c>
@@ -10631,7 +10631,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="293" spans="1:8">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A293" t="s">
         <v>95</v>
       </c>
@@ -10651,7 +10651,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="294" spans="1:8">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A294" t="s">
         <v>95</v>
       </c>
@@ -10671,7 +10671,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="295" spans="1:8">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A295" t="s">
         <v>95</v>
       </c>
@@ -10691,7 +10691,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="296" spans="1:8">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A296" t="s">
         <v>95</v>
       </c>
@@ -10711,7 +10711,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="297" spans="1:8">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A297" t="s">
         <v>95</v>
       </c>
@@ -10731,7 +10731,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="298" spans="1:8">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A298" t="s">
         <v>95</v>
       </c>
@@ -10751,7 +10751,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="299" spans="1:8">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A299" t="s">
         <v>130</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="300" spans="1:8">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A300" t="s">
         <v>130</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:8">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A301" t="s">
         <v>130</v>
       </c>
@@ -10829,7 +10829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:8">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A302" t="s">
         <v>130</v>
       </c>
@@ -10855,7 +10855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="1:8">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A303" t="s">
         <v>130</v>
       </c>
@@ -10881,7 +10881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="304" spans="1:8">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A304" t="s">
         <v>130</v>
       </c>
@@ -10907,7 +10907,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="305" spans="1:8">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A305" t="s">
         <v>130</v>
       </c>
@@ -10927,7 +10927,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="306" spans="1:8">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A306" t="s">
         <v>130</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="307" spans="1:8">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A307" t="s">
         <v>130</v>
       </c>
@@ -10967,7 +10967,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="308" spans="1:8">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A308" t="s">
         <v>130</v>
       </c>
@@ -10987,7 +10987,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="309" spans="1:8">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A309" t="s">
         <v>130</v>
       </c>
@@ -11007,7 +11007,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="310" spans="1:8">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A310" t="s">
         <v>130</v>
       </c>
@@ -11027,7 +11027,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="311" spans="1:8">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A311" t="s">
         <v>130</v>
       </c>
@@ -11047,7 +11047,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="312" spans="1:8">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A312" t="s">
         <v>130</v>
       </c>
@@ -11067,7 +11067,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="313" spans="1:8">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A313" t="s">
         <v>130</v>
       </c>
@@ -11087,7 +11087,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="314" spans="1:8">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A314" t="s">
         <v>130</v>
       </c>
@@ -11107,7 +11107,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="315" spans="1:8">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A315" t="s">
         <v>133</v>
       </c>
@@ -11133,7 +11133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="1:8">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A316" t="s">
         <v>133</v>
       </c>
@@ -11159,7 +11159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="1:8">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A317" t="s">
         <v>133</v>
       </c>
@@ -11185,7 +11185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="1:8">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A318" t="s">
         <v>133</v>
       </c>
@@ -11211,7 +11211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="1:8">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A319" t="s">
         <v>133</v>
       </c>
@@ -11237,7 +11237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:8">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A320" t="s">
         <v>133</v>
       </c>
@@ -11263,7 +11263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:8">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A321" t="s">
         <v>133</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="1:8">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A322" t="s">
         <v>133</v>
       </c>
@@ -11315,7 +11315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:8">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A323" t="s">
         <v>133</v>
       </c>
@@ -11335,7 +11335,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="324" spans="1:8">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A324" t="s">
         <v>133</v>
       </c>
@@ -11355,7 +11355,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="325" spans="1:8">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A325" t="s">
         <v>133</v>
       </c>
@@ -11375,7 +11375,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="326" spans="1:8">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A326" t="s">
         <v>133</v>
       </c>
@@ -11395,7 +11395,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="327" spans="1:8">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A327" t="s">
         <v>133</v>
       </c>
@@ -11415,7 +11415,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="328" spans="1:8">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A328" t="s">
         <v>133</v>
       </c>
@@ -11435,7 +11435,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="329" spans="1:8">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A329" t="s">
         <v>133</v>
       </c>
@@ -11455,7 +11455,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="330" spans="1:8">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A330" t="s">
         <v>133</v>
       </c>
@@ -11475,7 +11475,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="331" spans="1:8">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A331" t="s">
         <v>133</v>
       </c>
@@ -11495,7 +11495,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="332" spans="1:8">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A332" t="s">
         <v>133</v>
       </c>
@@ -11515,7 +11515,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="333" spans="1:8">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A333" t="s">
         <v>137</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:8">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A334" t="s">
         <v>137</v>
       </c>
@@ -11567,7 +11567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335" spans="1:8">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A335" t="s">
         <v>137</v>
       </c>
@@ -11593,7 +11593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="1:8">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A336" t="s">
         <v>137</v>
       </c>
@@ -11619,7 +11619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="1:8">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A337" t="s">
         <v>137</v>
       </c>
@@ -11645,7 +11645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="338" spans="1:8">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A338" t="s">
         <v>137</v>
       </c>
@@ -11671,7 +11671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339" spans="1:8">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A339" t="s">
         <v>137</v>
       </c>
@@ -11697,7 +11697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:8">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A340" t="s">
         <v>137</v>
       </c>
@@ -11723,7 +11723,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="341" spans="1:8">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A341" t="s">
         <v>137</v>
       </c>
@@ -11743,7 +11743,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="342" spans="1:8">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A342" t="s">
         <v>137</v>
       </c>
@@ -11763,7 +11763,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="343" spans="1:8">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A343" t="s">
         <v>137</v>
       </c>
@@ -11783,7 +11783,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="344" spans="1:8">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A344" t="s">
         <v>137</v>
       </c>
@@ -11803,7 +11803,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="345" spans="1:8">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A345" t="s">
         <v>137</v>
       </c>
@@ -11823,7 +11823,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="346" spans="1:8">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A346" t="s">
         <v>137</v>
       </c>
@@ -11843,7 +11843,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="347" spans="1:8">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A347" t="s">
         <v>137</v>
       </c>
@@ -11863,7 +11863,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="348" spans="1:8">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A348" t="s">
         <v>137</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="349" spans="1:8">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A349" t="s">
         <v>137</v>
       </c>
@@ -11903,7 +11903,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="350" spans="1:8">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A350" t="s">
         <v>137</v>
       </c>
@@ -11923,7 +11923,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="351" spans="1:8">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A351" t="s">
         <v>140</v>
       </c>
@@ -11949,7 +11949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="352" spans="1:8">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A352" t="s">
         <v>140</v>
       </c>
@@ -11975,7 +11975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="353" spans="1:8">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A353" t="s">
         <v>140</v>
       </c>
@@ -12001,7 +12001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="354" spans="1:8">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A354" t="s">
         <v>140</v>
       </c>
@@ -12027,7 +12027,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="355" spans="1:8">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A355" t="s">
         <v>140</v>
       </c>
@@ -12053,7 +12053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="356" spans="1:8">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A356" t="s">
         <v>140</v>
       </c>
@@ -12079,7 +12079,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="357" spans="1:8">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A357" t="s">
         <v>140</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="358" spans="1:8">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A358" t="s">
         <v>140</v>
       </c>
@@ -12119,7 +12119,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="359" spans="1:8">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A359" t="s">
         <v>140</v>
       </c>
@@ -12139,7 +12139,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="360" spans="1:8">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A360" t="s">
         <v>140</v>
       </c>
@@ -12159,7 +12159,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="361" spans="1:8">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A361" t="s">
         <v>140</v>
       </c>
@@ -12179,7 +12179,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="362" spans="1:8">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A362" t="s">
         <v>140</v>
       </c>
@@ -12199,7 +12199,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="363" spans="1:8">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A363" t="s">
         <v>140</v>
       </c>
@@ -12219,7 +12219,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="364" spans="1:8">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A364" t="s">
         <v>140</v>
       </c>
@@ -12239,7 +12239,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="365" spans="1:8">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A365" t="s">
         <v>140</v>
       </c>
@@ -12259,7 +12259,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="366" spans="1:8">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A366" t="s">
         <v>820</v>
       </c>
@@ -12279,7 +12279,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="367" spans="1:8">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A367" t="s">
         <v>823</v>
       </c>
@@ -12299,7 +12299,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="368" spans="1:8">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.1">
       <c r="A368" t="s">
         <v>826</v>
       </c>
@@ -12319,7 +12319,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A369" t="s">
         <v>826</v>
       </c>
@@ -12339,7 +12339,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A370" t="s">
         <v>826</v>
       </c>
@@ -12359,7 +12359,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A371" t="s">
         <v>833</v>
       </c>
@@ -12379,7 +12379,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A372" t="s">
         <v>833</v>
       </c>
@@ -12399,7 +12399,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A373" t="s">
         <v>837</v>
       </c>
@@ -12419,7 +12419,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="374" spans="1:7">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A374" t="s">
         <v>840</v>
       </c>
@@ -12439,7 +12439,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="375" spans="1:7">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A375" t="s">
         <v>840</v>
       </c>
@@ -12459,7 +12459,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A376" t="s">
         <v>840</v>
       </c>
@@ -12479,7 +12479,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="377" spans="1:7">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A377" t="s">
         <v>840</v>
       </c>
@@ -12499,7 +12499,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A378" t="s">
         <v>847</v>
       </c>
@@ -12519,7 +12519,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A379" t="s">
         <v>847</v>
       </c>
@@ -12539,7 +12539,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="380" spans="1:7">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A380" t="s">
         <v>847</v>
       </c>
@@ -12559,7 +12559,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="381" spans="1:7">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A381" t="s">
         <v>847</v>
       </c>
@@ -12579,7 +12579,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A382" t="s">
         <v>847</v>
       </c>
@@ -12599,7 +12599,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A383" t="s">
         <v>847</v>
       </c>
@@ -12619,7 +12619,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A384" t="s">
         <v>847</v>
       </c>
@@ -12639,7 +12639,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A385" t="s">
         <v>847</v>
       </c>
@@ -12659,7 +12659,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A386" t="s">
         <v>847</v>
       </c>
@@ -12679,7 +12679,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A387" t="s">
         <v>847</v>
       </c>
@@ -12699,7 +12699,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A388" t="s">
         <v>847</v>
       </c>
@@ -12719,7 +12719,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A389" t="s">
         <v>847</v>
       </c>
@@ -12739,7 +12739,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A390" t="s">
         <v>847</v>
       </c>
@@ -12759,7 +12759,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A391" t="s">
         <v>847</v>
       </c>
@@ -12779,7 +12779,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.1">
       <c r="A392" t="s">
         <v>847</v>
       </c>
@@ -12808,9 +12808,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA02B1F-9C6A-F043-8E69-5FE5B9EB8AD5}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+  <cols>
+    <col min="14" max="14" width="65.99609375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="60" customHeight="1">
+    <row r="1" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.1">
       <c r="A1" s="19" t="s">
         <v>875</v>
       </c>
@@ -12828,9 +12831,9 @@
       <c r="M1" s="20"/>
       <c r="N1" s="20"/>
     </row>
-    <row r="2" spans="1:14" ht="409" customHeight="1">
+    <row r="2" spans="1:14" ht="408.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="21" t="str" cm="1">
-        <f t="array" ref="A2">_xlfn.TEXTJOIN(",", TRUE, IF(emp_no!C2:INDEX(emp_no!C:C, LOOKUP(2,1/(emp_no!C:C&lt;&gt;""), ROW(emp_no!C:C)))&lt;&gt;"", "000"&amp;emp_no!C2:INDEX(emp_no!C:C, LOOKUP(2,1/(emp_no!C:C&lt;&gt;""), ROW(emp_no!C:C))), ""))</f>
+        <f t="array" aca="1" ref="A2" ca="1">_xlfn.TEXTJOIN(",", TRUE, IF(emp_no!C2:INDEX(emp_no!C:C, LOOKUP(2,1/(emp_no!C:C&lt;&gt;""), ROW(emp_no!C:C)))&lt;&gt;"", "000"&amp;emp_no!C2:INDEX(emp_no!C:C, LOOKUP(2,1/(emp_no!C:C&lt;&gt;""), ROW(emp_no!C:C))), ""))</f>
         <v>00039680,00049147,00041511,00046107,00041672,00045104,00038579,00041492,00041478,00041331,00041271,00041675,00042420,00045105,00048688,00038564,00041571,00041333,00050842,00045585,00041554,00041339,00041371,00041850,00042072,00049580,00040592,00041334,00036758,00041205,00041512,00041493,00043014,00044484,00046104,00053806,00042725,00044009,00044007,00045117,00048783,00039615,00049043,00039645,00041268,00041668,00044005,00048143,00036756,00036777,00037756,00037761,00048687,00040593,00049290,00041396,00041556,00041337,00049148,00041498,00042073,00041507,00042075,00044397,00042422,00043854,00043861,00040618,00040568,00038587,00041685,00067838,00047991,00036147,00037243,00038260,00039243,00037741,00037726,00037750,00039617,00038569,00038593,00042244,00048673,00048684,00041317,00041323,00041661,00049111,00043652,00044966,00037706,00067673,00067393,00067851,00067904,00036184,00037238,00039665,00039684,00041283,00049121,00041484,00053747,00035740,00035216,00037743,00037732,00041486,00052461,00056911,00055023,00056895,00052215,00053894,00052029,00036963,00039238,00039668,00042423,00053768,00053787,00046043,00050843,00051138,00052467,00055022,00057515,00056893,00053861,00052212,00053803,00036185,00053733,00039671,00048682,00049136,00053759,00053849,00045116,00045154,00054386,00058950,00056900,00057462,00053807,00052196,00052209,00045618,00036965,00040560,00041304,00049411,00042084,00041705,00044415,00053816,00045589,00045960,00056565,00054373,00055007,00056894,00057472,00052193,00044492,00052011,00067337,00037698,00040781,00053740,00040612,00042419,00045108,00045152,00050880,00051140,00057243,00055045,00056896,00057464,00053858,00052213,00053901,00041666,00044490,00037716,00039646,00038575,00040620,00043461,00042247,00045586,00045619,00045950,00054376,00058951,00056866,00052189,00052586,00045588,00052031,00036150,00036968,00049074,00039673,00040624,00041181,00053767,00044962,00045587,00041206,00056581,00055025,00056873,00057449,00053855,00052211,00053902,00051354,00039630,00037763,00039667,00053735,00041191,00041703,00044983,00045151,00045621,00054377,00055013,00057497,00053857,00052214,00045150,00050879,00053805,00067836,00039611,00040970,00039633,00040611,00041742,00046041,00045957,00054378,00056853,00056865,00057498,00052191,00052207,00052587,00035738,00038568,00039683,00041187,00053781,00041696,00044388,00044975,00044493,00052012,00056617,00054367,00056912,00056864,00056860,00053863,00053898,00051139,00048174,00040790,00048678,00040563,00053732,00050290,00044977,00050841,00051355,00054374,00056877,00058953,00053860,00052210,00053895,00051290,00036754,00038537,00038546,00048680,00053742,00041325,00044974,00046106,00046039,00051289,00052465,00055050,00056876,00057490,00052190,00049582,00053802,00036971,00037729,00038583,00041188,00049410,00042724,00044950,00045115,00045584,00056692,00057247,00055044,00056862,00056882,00057511,00052188,00053892,00053810,00067852,00035737,00040259,00038559,00041468,00044952,00045593,00045149,00045617,00052463,00056849,00054381,00057244,00056906,00057459,00052192,00052030,00067753,00038262,00039357,00049155,00049394,00049332,00044530,00045118,00050881,00045616,00054385,00055036,00058952,00053859,00052195,00052032,00048026,00049047,00040783,00048691,00053739,00043862,00044486,00046040,00051326,00040973,00040599,00044396,00045113,00051291,00041336,00045114,00038590,00036748,00039641,00039681,00039629,00041204,00048993,00040269,00044394,00057451,00056897,00057454,00057471,00057510,00057483,00057460,00058367,00053896,00057475,00057484</v>
       </c>
       <c r="B2" s="21"/>
@@ -12860,9 +12863,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -12876,7 +12879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -12890,7 +12893,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A3" t="s">
         <v>9</v>
       </c>
